--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104591_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104591_W15.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2935</v>
+        <v>7.4507</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4726</v>
+        <v>6.5707</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8209</v>
+        <v>0.88</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0739</v>
+        <v>5.0734</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6345</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4434</v>
+        <v>4.4389</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0855</v>
+        <v>6.0623</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0953</v>
+        <v>2.0857</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9902</v>
+        <v>3.9767</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0116</v>
+        <v>-0.989</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6318</v>
+        <v>0.7839</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3871</v>
+        <v>0.5084</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2447</v>
+        <v>0.2755</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8431</v>
+        <v>5.8982</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4443</v>
+        <v>5.7424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3988</v>
+        <v>0.1558</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1829</v>
+        <v>4.12</v>
       </c>
       <c r="H3" t="n">
-        <v>1.544</v>
+        <v>1.7638</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6389</v>
+        <v>2.3562</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6882</v>
+        <v>4.9947</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3075</v>
+        <v>2.9992</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3807</v>
+        <v>1.9955</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5053</v>
+        <v>-0.8747</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7635</v>
+        <v>-1.2355</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2582</v>
+        <v>0.3608</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2992</v>
+        <v>-0.2916</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8903</v>
+        <v>-0.3417</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4089</v>
+        <v>0.0501</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5601</v>
+        <v>5.5452</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6838</v>
+        <v>5.4317</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1237</v>
+        <v>0.1135</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6327</v>
+        <v>4.6278</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3492</v>
+        <v>-0.3503</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9818</v>
+        <v>4.9781</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0185</v>
+        <v>4.9998</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3912</v>
+        <v>0.3825</v>
       </c>
       <c r="L4" t="n">
-        <v>4.6273</v>
+        <v>4.6174</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3858</v>
+        <v>-0.372</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3396</v>
+        <v>0.324</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6654</v>
+        <v>0.4319</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3257</v>
+        <v>-0.1078</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3895</v>
+        <v>5.3319</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3974</v>
+        <v>4.623</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9921</v>
+        <v>0.7089</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9405</v>
+        <v>4.3993</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7117</v>
+        <v>0.3881</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2289</v>
+        <v>4.0113</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6545</v>
+        <v>4.7161</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4679</v>
+        <v>1.9683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1866</v>
+        <v>2.7479</v>
       </c>
       <c r="M5" t="n">
-        <v>0.286</v>
+        <v>-0.3168</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7563</v>
+        <v>-1.5802</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0423</v>
+        <v>1.2634</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1976</v>
+        <v>0.2009</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2381</v>
+        <v>-0.0931</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0405</v>
+        <v>0.294</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4783</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3354</v>
+        <v>4.4409</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4199</v>
+        <v>4.0797</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0844</v>
+        <v>0.3611</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1334</v>
+        <v>4.1809</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7691</v>
+        <v>1.5397</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3643</v>
+        <v>2.6412</v>
       </c>
       <c r="J6" t="n">
-        <v>5.0228</v>
+        <v>4.67</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0131</v>
+        <v>3.2922</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0097</v>
+        <v>1.3778</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8894</v>
+        <v>-0.4891</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.244</v>
+        <v>-1.7526</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>1.2634</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8641</v>
+        <v>0.8942</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6956</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1685</v>
+        <v>0.3463</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.1217</v>
+        <v>4.2061</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3438</v>
+        <v>3.0678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7779</v>
+        <v>1.1384</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4109</v>
+        <v>1.9284</v>
       </c>
       <c r="H7" t="n">
-        <v>0.394</v>
+        <v>0.6932</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0169</v>
+        <v>1.2352</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7431</v>
+        <v>1.6266</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9843</v>
+        <v>1.4404</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7587</v>
+        <v>0.1862</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3321</v>
+        <v>0.3018</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5903</v>
+        <v>-0.7472</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2582</v>
+        <v>1.049</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0112</v>
+        <v>1.029</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3992</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.388</v>
+        <v>0.0838</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>1.4764</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7451</v>
+        <v>1.9913</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7111</v>
+        <v>1.0039</v>
       </c>
       <c r="F8" t="n">
-        <v>1.034</v>
+        <v>0.9875</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3563</v>
+        <v>0.3538</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7041</v>
+        <v>-1.7032</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0604</v>
+        <v>2.057</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9712</v>
+        <v>0.9576</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5585</v>
+        <v>-1.5513</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.199</v>
+        <v>0.0441</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2601</v>
+        <v>0.0463</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0611</v>
+        <v>-0.0022</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5644</v>
+        <v>1.5147</v>
       </c>
       <c r="E9" t="n">
+        <v>1.5615</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.3487</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.2157</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.3495</v>
-      </c>
       <c r="H9" t="n">
-        <v>1.4748</v>
+        <v>1.4707</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1253</v>
+        <v>-0.122</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3485</v>
+        <v>2.338</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1992</v>
+        <v>2.1891</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.999</v>
+        <v>-0.9893</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5078</v>
+        <v>0.4634</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8556</v>
+        <v>0.575</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2229</v>
+        <v>1.4825</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3944</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8286</v>
+        <v>0.5647</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8905</v>
+        <v>0.8889</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9349</v>
+        <v>-1.9385</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8255</v>
+        <v>2.8274</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5799</v>
+        <v>1.5636</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9405</v>
+        <v>1.9363</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6894</v>
+        <v>-0.6747</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5744</v>
+        <v>-1.5658</v>
       </c>
       <c r="O10" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5592</v>
+        <v>0.8212</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0514</v>
+        <v>0.4923</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6106</v>
+        <v>0.3289</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9371</v>
+        <v>-0.3414</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0598</v>
+        <v>-0.3091</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1227</v>
+        <v>-0.0323</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8719</v>
+        <v>-0.8707</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4445</v>
+        <v>-2.436</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5726</v>
+        <v>1.5653</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2433</v>
+        <v>0.2209</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0275</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2158</v>
+        <v>0.2004</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1152</v>
+        <v>-1.0916</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.472</v>
+        <v>-2.4565</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3568</v>
+        <v>1.3648</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1863</v>
+        <v>0.7782</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3297</v>
+        <v>0.4504</v>
       </c>
       <c r="U11" t="n">
-        <v>0.516</v>
+        <v>0.3278</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9876</v>
+        <v>-0.6121</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3282</v>
+        <v>-0.6988</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3406</v>
+        <v>0.0867</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0087</v>
+        <v>-0.1882</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8008</v>
+        <v>-2.2748</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2079</v>
+        <v>2.0866</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9852</v>
+        <v>0.1562</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4227</v>
+        <v>-1.3552</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5625</v>
+        <v>1.5114</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0236</v>
+        <v>-0.3444</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3781</v>
+        <v>-0.9196</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3546</v>
+        <v>0.5752</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1642</v>
+        <v>0.5958</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2601</v>
+        <v>0.2832</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0959</v>
+        <v>0.3126</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3685</v>
+        <v>-0.7801</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1477</v>
+        <v>-1.2331</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2208</v>
+        <v>0.4529</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.182</v>
+        <v>-1.0067</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.277</v>
+        <v>-0.8013</v>
       </c>
       <c r="I13" t="n">
-        <v>2.095</v>
+        <v>-0.2055</v>
       </c>
       <c r="J13" t="n">
-        <v>0.177</v>
+        <v>-0.9939</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3476</v>
+        <v>-0.4277</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5246</v>
+        <v>-0.5662</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.359</v>
+        <v>-0.0129</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9294</v>
+        <v>-0.3736</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5705</v>
+        <v>0.3608</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.16</v>
+        <v>0.0476</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1905</v>
+        <v>-0.1418</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0305</v>
+        <v>0.1895</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>35.78250000000001</v>
+        <v>36.1279</v>
       </c>
       <c r="E14" t="n">
-        <v>30.6803</v>
+        <v>30.75750000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>5.1024</v>
+        <v>5.3703</v>
       </c>
       <c r="G14" t="n">
-        <v>24.908</v>
+        <v>24.8556</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.9864</v>
+        <v>-3.0141</v>
       </c>
       <c r="I14" t="n">
-        <v>27.8945</v>
+        <v>27.8697</v>
       </c>
       <c r="J14" t="n">
-        <v>31.5473</v>
+        <v>31.3119</v>
       </c>
       <c r="K14" t="n">
-        <v>12.2096</v>
+        <v>12.0704</v>
       </c>
       <c r="L14" t="n">
-        <v>19.3377</v>
+        <v>19.2417</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.6393</v>
+        <v>-6.4564</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.1962</v>
+        <v>-15.0846</v>
       </c>
       <c r="O14" t="n">
-        <v>8.557099999999998</v>
+        <v>8.6281</v>
       </c>
       <c r="P14" t="n">
-        <v>6.8051</v>
+        <v>6.8291</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.073500000000001</v>
+        <v>-9.105500000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S14" t="n">
-        <v>5.323</v>
+        <v>5.6907</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6465</v>
+        <v>3.017300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6766</v>
+        <v>2.6735</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W14" t="n">
-        <v>5.559899999999999</v>
+        <v>5.5337</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.8133</v>
+        <v>-6.781</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4181</v>
+        <v>0.7603</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4809</v>
+        <v>4.5947</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.0628</v>
+        <v>-3.8344</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0547</v>
+        <v>-1.0643</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7793</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8339</v>
+        <v>-1.8399</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4349</v>
+        <v>3.3931</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1099</v>
+        <v>3.0887</v>
       </c>
       <c r="L15" t="n">
-        <v>0.325</v>
+        <v>0.3045</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.4896</v>
+        <v>-4.4574</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.3307</v>
+        <v>-2.313</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5804</v>
+        <v>-0.0569</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8075</v>
+        <v>-0.0166</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2271</v>
+        <v>-0.0403</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3433</v>
+        <v>0.7071</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8392</v>
+        <v>2.065</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4959</v>
+        <v>-1.3579</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6953</v>
+        <v>0.6978</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4257</v>
+        <v>1.4246</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.7268</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2565</v>
+        <v>2.2463</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1819</v>
+        <v>2.1718</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5612</v>
+        <v>-1.5485</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5789</v>
+        <v>-0.2184</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1615</v>
+        <v>-0.037</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5974</v>
+        <v>-0.5289</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1741</v>
+        <v>-0.1746</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4234</v>
+        <v>-0.3543</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7435</v>
+        <v>-0.7391</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0028</v>
+        <v>0.0056</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7781</v>
+        <v>-0.7736</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0808</v>
+        <v>-0.0174</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1279</v>
+        <v>0.1917</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6966</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.804</v>
+        <v>-0.8076</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1073</v>
+        <v>0.1105</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9235</v>
+        <v>-0.9247</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1371</v>
+        <v>-0.1351</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="K18" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0696</v>
+        <v>0.0697</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6806</v>
+        <v>-1.7722</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2394</v>
+        <v>0.2174</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.92</v>
+        <v>-1.9896</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.686</v>
+        <v>-1.684</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2251</v>
+        <v>0.2241</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9112</v>
+        <v>-1.9081</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6155</v>
+        <v>1.5973</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3016</v>
+        <v>-3.2813</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.3563</v>
+        <v>-2.3472</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4482</v>
+        <v>-0.5435</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6956</v>
+        <v>-0.697</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2474</v>
+        <v>0.1535</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2708</v>
+        <v>-2.3238</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7498</v>
+        <v>-0.7577</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.521</v>
+        <v>-1.566</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4559</v>
+        <v>-2.4472</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2915</v>
+        <v>-0.2874</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1644</v>
+        <v>-2.1597</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1056</v>
+        <v>-0.1119</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3503</v>
+        <v>-2.3353</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6542</v>
+        <v>-0.7188</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2368</v>
+        <v>-0.3006</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9792</v>
+        <v>-3.2857</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3276</v>
+        <v>1.6998</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.3068</v>
+        <v>-4.9855</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0061</v>
+        <v>-1.9977</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1601</v>
+        <v>2.1625</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.1662</v>
+        <v>-4.1602</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6726</v>
+        <v>2.6465</v>
       </c>
       <c r="K21" t="n">
-        <v>4.208</v>
+        <v>4.1886</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.6787</v>
+        <v>-4.6442</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0479</v>
+        <v>-2.026</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.6308</v>
+        <v>-2.6182</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2952</v>
+        <v>-0.0117</v>
       </c>
       <c r="T21" t="n">
-        <v>0.738</v>
+        <v>0.1506</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4428</v>
+        <v>-0.1623</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2352</v>
+        <v>-4.7089</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.203</v>
+        <v>-1.871</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0322</v>
+        <v>-2.8379</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2004</v>
+        <v>-1.1865</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2569</v>
+        <v>-0.253</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9435</v>
+        <v>-0.9335</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7575</v>
+        <v>0.7472</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7202</v>
+        <v>0.71</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9579</v>
+        <v>-1.9337</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8741</v>
+        <v>-0.3646</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.248</v>
+        <v>-0.0926</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2989</v>
+        <v>-6.4779</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5553</v>
+        <v>-1.9891</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7436</v>
+        <v>-4.4888</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.0492</v>
+        <v>-5.0365</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8457</v>
+        <v>-0.839</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2035</v>
+        <v>-4.1975</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7486</v>
+        <v>-0.7659</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8134</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.3006</v>
+        <v>-4.2706</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.6308</v>
+        <v>-2.6182</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2497</v>
+        <v>-0.4414</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7652</v>
+        <v>-0.1745</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4845</v>
+        <v>-0.2669</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6473</v>
+        <v>-7.3614</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6237</v>
+        <v>-3.7747</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.0236</v>
+        <v>-3.5867</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.5474</v>
+        <v>-4.5458</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3274</v>
+        <v>1.3324</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.8748</v>
+        <v>-5.8782</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1713</v>
+        <v>-1.1936</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9741</v>
+        <v>1.965</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.1454</v>
+        <v>-3.1586</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.3761</v>
+        <v>-3.3522</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.7294</v>
+        <v>-2.7196</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.2905</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1179</v>
+        <v>-0.2349</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4621</v>
+        <v>-0.0556</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.138</v>
+        <v>-8.5116</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8796</v>
+        <v>-4.5724</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.2584</v>
+        <v>-3.9392</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.9367</v>
+        <v>-5.9275</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4027</v>
+        <v>-1.3962</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.534</v>
+        <v>-4.5313</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.3726</v>
+        <v>-1.3991</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3148</v>
+        <v>0.2995</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.5641</v>
+        <v>-4.5283</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7175</v>
+        <v>-1.6957</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.8467</v>
+        <v>-2.8326</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7327</v>
+        <v>-1.0998</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8284</v>
+        <v>-0.549</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-35.7826</v>
+        <v>-34.2001</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.102399999999999</v>
+        <v>-5.370200000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-30.68040000000001</v>
+        <v>-28.8298</v>
       </c>
       <c r="G26" t="n">
-        <v>-24.9081</v>
+        <v>-24.8555</v>
       </c>
       <c r="H26" t="n">
-        <v>2.986499999999999</v>
+        <v>3.0142</v>
       </c>
       <c r="I26" t="n">
-        <v>-27.8945</v>
+        <v>-27.8695</v>
       </c>
       <c r="J26" t="n">
-        <v>6.639099999999999</v>
+        <v>6.456499999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>15.1961</v>
+        <v>15.0846</v>
       </c>
       <c r="L26" t="n">
-        <v>-8.557</v>
+        <v>-8.628</v>
       </c>
       <c r="M26" t="n">
-        <v>-31.5473</v>
+        <v>-31.31189999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-12.2098</v>
+        <v>-12.0702</v>
       </c>
       <c r="O26" t="n">
-        <v>-19.3377</v>
+        <v>-19.2415</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.805099999999999</v>
+        <v>-6.829099999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8784</v>
+        <v>-15.9341</v>
       </c>
       <c r="R26" t="n">
-        <v>9.073300000000001</v>
+        <v>9.1053</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.3231</v>
+        <v>-3.763</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.6767</v>
+        <v>-2.6735</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.6463</v>
+        <v>-1.0894</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W26" t="n">
-        <v>6.813200000000001</v>
+        <v>6.7809</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.56</v>
+        <v>-5.533700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104591_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104591_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.781</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104591_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.533700000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
